--- a/docs/pension_data_combined_2026-09-25.xlsx
+++ b/docs/pension_data_combined_2026-09-25.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1797</v>
-      </c>
       <c r="D48" t="n">
         <v>4228905.67</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-09-25</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.184</v>
       </c>
       <c r="D55" t="n">
         <v>58670095.74</v>
